--- a/artfynd/A 10372-2025 artfynd.xlsx
+++ b/artfynd/A 10372-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819045</v>
+        <v>123819049</v>
       </c>
       <c r="B2" t="n">
-        <v>94807</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497270</v>
+        <v>497080</v>
       </c>
       <c r="R2" t="n">
-        <v>6373300</v>
+        <v>6373345</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819041</v>
+        <v>123819039</v>
       </c>
       <c r="B3" t="n">
-        <v>91603</v>
+        <v>74862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497150</v>
+        <v>497240</v>
       </c>
       <c r="R3" t="n">
-        <v>6373570</v>
+        <v>6373483</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819042</v>
+        <v>123819045</v>
       </c>
       <c r="B4" t="n">
-        <v>90948</v>
+        <v>94813</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497190</v>
+        <v>497270</v>
       </c>
       <c r="R4" t="n">
-        <v>6373593</v>
+        <v>6373300</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819050</v>
+        <v>123819044</v>
       </c>
       <c r="B5" t="n">
-        <v>74867</v>
+        <v>105518</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497232</v>
+        <v>497237</v>
       </c>
       <c r="R5" t="n">
-        <v>6373400</v>
+        <v>6373460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819044</v>
+        <v>123819041</v>
       </c>
       <c r="B6" t="n">
-        <v>105502</v>
+        <v>91608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497237</v>
+        <v>497150</v>
       </c>
       <c r="R6" t="n">
-        <v>6373460</v>
+        <v>6373570</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819039</v>
+        <v>123819043</v>
       </c>
       <c r="B7" t="n">
-        <v>74859</v>
+        <v>90953</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497240</v>
+        <v>497237</v>
       </c>
       <c r="R7" t="n">
-        <v>6373483</v>
+        <v>6373460</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819055</v>
+        <v>123819040</v>
       </c>
       <c r="B8" t="n">
-        <v>4776</v>
+        <v>5176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,27 +1303,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497235</v>
+        <v>497225</v>
       </c>
       <c r="R8" t="n">
-        <v>6373313</v>
+        <v>6373525</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819049</v>
+        <v>123819048</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497080</v>
+        <v>497275</v>
       </c>
       <c r="R9" t="n">
-        <v>6373345</v>
+        <v>6373290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819048</v>
+        <v>123819050</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>74870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497275</v>
+        <v>497232</v>
       </c>
       <c r="R10" t="n">
-        <v>6373290</v>
+        <v>6373400</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819040</v>
+        <v>123819055</v>
       </c>
       <c r="B11" t="n">
-        <v>5174</v>
+        <v>4778</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,27 +1614,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497225</v>
+        <v>497235</v>
       </c>
       <c r="R11" t="n">
-        <v>6373525</v>
+        <v>6373313</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
         <v>123819054</v>
       </c>
       <c r="B12" t="n">
-        <v>5194</v>
+        <v>5196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819043</v>
+        <v>123819042</v>
       </c>
       <c r="B13" t="n">
-        <v>90948</v>
+        <v>90953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497237</v>
+        <v>497190</v>
       </c>
       <c r="R13" t="n">
-        <v>6373460</v>
+        <v>6373593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 10372-2025 artfynd.xlsx
+++ b/artfynd/A 10372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123819049</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819039</v>
+        <v>123819050</v>
       </c>
       <c r="B3" t="n">
-        <v>74862</v>
+        <v>74871</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497240</v>
+        <v>497232</v>
       </c>
       <c r="R3" t="n">
-        <v>6373483</v>
+        <v>6373400</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819045</v>
+        <v>123819055</v>
       </c>
       <c r="B4" t="n">
-        <v>94813</v>
+        <v>4778</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497270</v>
+        <v>497235</v>
       </c>
       <c r="R4" t="n">
-        <v>6373300</v>
+        <v>6373313</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819044</v>
+        <v>123819054</v>
       </c>
       <c r="B5" t="n">
-        <v>105518</v>
+        <v>5196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497237</v>
+        <v>497222</v>
       </c>
       <c r="R5" t="n">
-        <v>6373460</v>
+        <v>6373306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819041</v>
+        <v>123819048</v>
       </c>
       <c r="B6" t="n">
-        <v>91608</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497150</v>
+        <v>497275</v>
       </c>
       <c r="R6" t="n">
-        <v>6373570</v>
+        <v>6373290</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819043</v>
+        <v>123819044</v>
       </c>
       <c r="B7" t="n">
-        <v>90953</v>
+        <v>105520</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819040</v>
+        <v>123819041</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>91610</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,42 +1313,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497225</v>
+        <v>497150</v>
       </c>
       <c r="R8" t="n">
-        <v>6373525</v>
+        <v>6373570</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819048</v>
+        <v>123819042</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>90955</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497275</v>
+        <v>497190</v>
       </c>
       <c r="R9" t="n">
-        <v>6373290</v>
+        <v>6373593</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819050</v>
+        <v>123819039</v>
       </c>
       <c r="B10" t="n">
-        <v>74870</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497232</v>
+        <v>497240</v>
       </c>
       <c r="R10" t="n">
-        <v>6373400</v>
+        <v>6373483</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819055</v>
+        <v>123819045</v>
       </c>
       <c r="B11" t="n">
-        <v>4778</v>
+        <v>94815</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,39 +1619,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497235</v>
+        <v>497270</v>
       </c>
       <c r="R11" t="n">
-        <v>6373313</v>
+        <v>6373300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819054</v>
+        <v>123819043</v>
       </c>
       <c r="B12" t="n">
-        <v>5196</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,39 +1721,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497222</v>
+        <v>497237</v>
       </c>
       <c r="R12" t="n">
-        <v>6373306</v>
+        <v>6373460</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819042</v>
+        <v>123819040</v>
       </c>
       <c r="B13" t="n">
-        <v>90953</v>
+        <v>5176</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,34 +1823,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497190</v>
+        <v>497225</v>
       </c>
       <c r="R13" t="n">
-        <v>6373593</v>
+        <v>6373525</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 10372-2025 artfynd.xlsx
+++ b/artfynd/A 10372-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819049</v>
+        <v>123819055</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>4778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497080</v>
+        <v>497235</v>
       </c>
       <c r="R2" t="n">
-        <v>6373345</v>
+        <v>6373313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819050</v>
+        <v>123819049</v>
       </c>
       <c r="B3" t="n">
-        <v>74871</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497232</v>
+        <v>497080</v>
       </c>
       <c r="R3" t="n">
-        <v>6373400</v>
+        <v>6373345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819055</v>
+        <v>123819041</v>
       </c>
       <c r="B4" t="n">
-        <v>4778</v>
+        <v>91610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497235</v>
+        <v>497150</v>
       </c>
       <c r="R4" t="n">
-        <v>6373313</v>
+        <v>6373570</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819054</v>
+        <v>123819048</v>
       </c>
       <c r="B5" t="n">
-        <v>5196</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497222</v>
+        <v>497275</v>
       </c>
       <c r="R5" t="n">
-        <v>6373306</v>
+        <v>6373290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819048</v>
+        <v>123819045</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>95323</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497275</v>
+        <v>497270</v>
       </c>
       <c r="R6" t="n">
-        <v>6373290</v>
+        <v>6373300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819044</v>
+        <v>123819043</v>
       </c>
       <c r="B7" t="n">
-        <v>105520</v>
+        <v>90955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819041</v>
+        <v>123819040</v>
       </c>
       <c r="B8" t="n">
-        <v>91610</v>
+        <v>5176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,37 +1308,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497150</v>
+        <v>497225</v>
       </c>
       <c r="R8" t="n">
-        <v>6373570</v>
+        <v>6373525</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819042</v>
+        <v>123819044</v>
       </c>
       <c r="B9" t="n">
-        <v>90955</v>
+        <v>105095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497190</v>
+        <v>497237</v>
       </c>
       <c r="R9" t="n">
-        <v>6373593</v>
+        <v>6373460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819045</v>
+        <v>123819042</v>
       </c>
       <c r="B11" t="n">
-        <v>94815</v>
+        <v>90955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497270</v>
+        <v>497190</v>
       </c>
       <c r="R11" t="n">
-        <v>6373300</v>
+        <v>6373593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819043</v>
+        <v>123819054</v>
       </c>
       <c r="B12" t="n">
-        <v>90955</v>
+        <v>5196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,34 +1721,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497237</v>
+        <v>497222</v>
       </c>
       <c r="R12" t="n">
-        <v>6373460</v>
+        <v>6373306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819040</v>
+        <v>123819050</v>
       </c>
       <c r="B13" t="n">
-        <v>5176</v>
+        <v>74871</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,43 +1824,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497225</v>
+        <v>497232</v>
       </c>
       <c r="R13" t="n">
-        <v>6373525</v>
+        <v>6373400</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 10372-2025 artfynd.xlsx
+++ b/artfynd/A 10372-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819055</v>
+        <v>123819041</v>
       </c>
       <c r="B2" t="n">
-        <v>4778</v>
+        <v>91610</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497235</v>
+        <v>497150</v>
       </c>
       <c r="R2" t="n">
-        <v>6373313</v>
+        <v>6373570</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819049</v>
+        <v>123819045</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>95323</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497080</v>
+        <v>497270</v>
       </c>
       <c r="R3" t="n">
-        <v>6373345</v>
+        <v>6373300</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819041</v>
+        <v>123819055</v>
       </c>
       <c r="B4" t="n">
-        <v>91610</v>
+        <v>4778</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497150</v>
+        <v>497235</v>
       </c>
       <c r="R4" t="n">
-        <v>6373570</v>
+        <v>6373313</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819048</v>
+        <v>123819040</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>5176</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +998,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497275</v>
+        <v>497225</v>
       </c>
       <c r="R5" t="n">
-        <v>6373290</v>
+        <v>6373525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819045</v>
+        <v>123819043</v>
       </c>
       <c r="B6" t="n">
-        <v>95323</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497270</v>
+        <v>497237</v>
       </c>
       <c r="R6" t="n">
-        <v>6373300</v>
+        <v>6373460</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819043</v>
+        <v>123819039</v>
       </c>
       <c r="B7" t="n">
-        <v>90955</v>
+        <v>74863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497237</v>
+        <v>497240</v>
       </c>
       <c r="R7" t="n">
-        <v>6373460</v>
+        <v>6373483</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819040</v>
+        <v>123819042</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>90955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,39 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497225</v>
+        <v>497190</v>
       </c>
       <c r="R8" t="n">
-        <v>6373525</v>
+        <v>6373593</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819039</v>
+        <v>123819048</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497240</v>
+        <v>497275</v>
       </c>
       <c r="R10" t="n">
-        <v>6373483</v>
+        <v>6373290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819042</v>
+        <v>123819049</v>
       </c>
       <c r="B11" t="n">
-        <v>90955</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497190</v>
+        <v>497080</v>
       </c>
       <c r="R11" t="n">
-        <v>6373593</v>
+        <v>6373345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 10372-2025 artfynd.xlsx
+++ b/artfynd/A 10372-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819041</v>
+        <v>123819043</v>
       </c>
       <c r="B2" t="n">
-        <v>91610</v>
+        <v>90955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497150</v>
+        <v>497237</v>
       </c>
       <c r="R2" t="n">
-        <v>6373570</v>
+        <v>6373460</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819045</v>
+        <v>123819050</v>
       </c>
       <c r="B3" t="n">
-        <v>95323</v>
+        <v>74871</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497270</v>
+        <v>497232</v>
       </c>
       <c r="R3" t="n">
-        <v>6373300</v>
+        <v>6373400</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819055</v>
+        <v>123819049</v>
       </c>
       <c r="B4" t="n">
-        <v>4778</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497235</v>
+        <v>497080</v>
       </c>
       <c r="R4" t="n">
-        <v>6373313</v>
+        <v>6373345</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819040</v>
+        <v>123819054</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,27 +997,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497225</v>
+        <v>497222</v>
       </c>
       <c r="R5" t="n">
-        <v>6373525</v>
+        <v>6373306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819043</v>
+        <v>123819041</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>91610</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497237</v>
+        <v>497150</v>
       </c>
       <c r="R6" t="n">
-        <v>6373460</v>
+        <v>6373570</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819039</v>
+        <v>123819055</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>4778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,34 +1206,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497240</v>
+        <v>497235</v>
       </c>
       <c r="R7" t="n">
-        <v>6373483</v>
+        <v>6373313</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819042</v>
+        <v>123819045</v>
       </c>
       <c r="B8" t="n">
-        <v>90955</v>
+        <v>95323</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497190</v>
+        <v>497270</v>
       </c>
       <c r="R8" t="n">
-        <v>6373593</v>
+        <v>6373300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819044</v>
+        <v>123819039</v>
       </c>
       <c r="B9" t="n">
-        <v>105095</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497237</v>
+        <v>497240</v>
       </c>
       <c r="R9" t="n">
-        <v>6373460</v>
+        <v>6373483</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819048</v>
+        <v>123819044</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497275</v>
+        <v>497237</v>
       </c>
       <c r="R10" t="n">
-        <v>6373290</v>
+        <v>6373460</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819049</v>
+        <v>123819040</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>5176</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,38 +1615,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497080</v>
+        <v>497225</v>
       </c>
       <c r="R11" t="n">
-        <v>6373345</v>
+        <v>6373525</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819054</v>
+        <v>123819042</v>
       </c>
       <c r="B12" t="n">
-        <v>5196</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,39 +1726,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497222</v>
+        <v>497190</v>
       </c>
       <c r="R12" t="n">
-        <v>6373306</v>
+        <v>6373593</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819050</v>
+        <v>123819048</v>
       </c>
       <c r="B13" t="n">
-        <v>74871</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497232</v>
+        <v>497275</v>
       </c>
       <c r="R13" t="n">
-        <v>6373400</v>
+        <v>6373290</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 10372-2025 artfynd.xlsx
+++ b/artfynd/A 10372-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819050</v>
+        <v>123819055</v>
       </c>
       <c r="B3" t="n">
-        <v>74871</v>
+        <v>4778</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497232</v>
+        <v>497235</v>
       </c>
       <c r="R3" t="n">
-        <v>6373400</v>
+        <v>6373313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819049</v>
+        <v>123819041</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>91610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497080</v>
+        <v>497150</v>
       </c>
       <c r="R4" t="n">
-        <v>6373345</v>
+        <v>6373570</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819054</v>
+        <v>123819048</v>
       </c>
       <c r="B5" t="n">
-        <v>5196</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497222</v>
+        <v>497275</v>
       </c>
       <c r="R5" t="n">
-        <v>6373306</v>
+        <v>6373290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819041</v>
+        <v>123819054</v>
       </c>
       <c r="B6" t="n">
-        <v>91610</v>
+        <v>5196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1104,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497150</v>
+        <v>497222</v>
       </c>
       <c r="R6" t="n">
-        <v>6373570</v>
+        <v>6373306</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819055</v>
+        <v>123819040</v>
       </c>
       <c r="B7" t="n">
-        <v>4778</v>
+        <v>5176</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,27 +1211,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497235</v>
+        <v>497225</v>
       </c>
       <c r="R7" t="n">
-        <v>6373313</v>
+        <v>6373525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819045</v>
+        <v>123819050</v>
       </c>
       <c r="B8" t="n">
-        <v>95323</v>
+        <v>74871</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497270</v>
+        <v>497232</v>
       </c>
       <c r="R8" t="n">
-        <v>6373300</v>
+        <v>6373400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819039</v>
+        <v>123819044</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>105095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497240</v>
+        <v>497237</v>
       </c>
       <c r="R9" t="n">
-        <v>6373483</v>
+        <v>6373460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819044</v>
+        <v>123819049</v>
       </c>
       <c r="B10" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497237</v>
+        <v>497080</v>
       </c>
       <c r="R10" t="n">
-        <v>6373460</v>
+        <v>6373345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819040</v>
+        <v>123819042</v>
       </c>
       <c r="B11" t="n">
-        <v>5176</v>
+        <v>90955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,39 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497225</v>
+        <v>497190</v>
       </c>
       <c r="R11" t="n">
-        <v>6373525</v>
+        <v>6373593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819042</v>
+        <v>123819045</v>
       </c>
       <c r="B12" t="n">
-        <v>90955</v>
+        <v>95323</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497190</v>
+        <v>497270</v>
       </c>
       <c r="R12" t="n">
-        <v>6373593</v>
+        <v>6373300</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819048</v>
+        <v>123819039</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497275</v>
+        <v>497240</v>
       </c>
       <c r="R13" t="n">
-        <v>6373290</v>
+        <v>6373483</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 10372-2025 artfynd.xlsx
+++ b/artfynd/A 10372-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819043</v>
+        <v>123819040</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>5176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497237</v>
+        <v>497225</v>
       </c>
       <c r="R2" t="n">
-        <v>6373460</v>
+        <v>6373525</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819041</v>
+        <v>123819049</v>
       </c>
       <c r="B4" t="n">
-        <v>91610</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497150</v>
+        <v>497080</v>
       </c>
       <c r="R4" t="n">
-        <v>6373570</v>
+        <v>6373345</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819048</v>
+        <v>123819044</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497275</v>
+        <v>497237</v>
       </c>
       <c r="R5" t="n">
-        <v>6373290</v>
+        <v>6373460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819054</v>
+        <v>123819039</v>
       </c>
       <c r="B6" t="n">
-        <v>5196</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497222</v>
+        <v>497240</v>
       </c>
       <c r="R6" t="n">
-        <v>6373306</v>
+        <v>6373483</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819040</v>
+        <v>123819045</v>
       </c>
       <c r="B7" t="n">
-        <v>5176</v>
+        <v>95323</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497225</v>
+        <v>497270</v>
       </c>
       <c r="R7" t="n">
-        <v>6373525</v>
+        <v>6373300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819044</v>
+        <v>123819054</v>
       </c>
       <c r="B9" t="n">
-        <v>105095</v>
+        <v>5196</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497237</v>
+        <v>497222</v>
       </c>
       <c r="R9" t="n">
-        <v>6373460</v>
+        <v>6373306</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819049</v>
+        <v>123819041</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>91610</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497080</v>
+        <v>497150</v>
       </c>
       <c r="R10" t="n">
-        <v>6373345</v>
+        <v>6373570</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819042</v>
+        <v>123819043</v>
       </c>
       <c r="B11" t="n">
         <v>90955</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497190</v>
+        <v>497237</v>
       </c>
       <c r="R11" t="n">
-        <v>6373593</v>
+        <v>6373460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819045</v>
+        <v>123819042</v>
       </c>
       <c r="B12" t="n">
-        <v>95323</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497270</v>
+        <v>497190</v>
       </c>
       <c r="R12" t="n">
-        <v>6373300</v>
+        <v>6373593</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819039</v>
+        <v>123819048</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497240</v>
+        <v>497275</v>
       </c>
       <c r="R13" t="n">
-        <v>6373483</v>
+        <v>6373290</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 10372-2025 artfynd.xlsx
+++ b/artfynd/A 10372-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819048</v>
+        <v>123819041</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497275</v>
+        <v>497150</v>
       </c>
       <c r="R2" t="n">
-        <v>6373290</v>
+        <v>6373570</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819039</v>
+        <v>123819049</v>
       </c>
       <c r="B3" t="n">
-        <v>74885</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497240</v>
+        <v>497080</v>
       </c>
       <c r="R3" t="n">
-        <v>6373483</v>
+        <v>6373345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819044</v>
+        <v>123819039</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>74885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497237</v>
+        <v>497240</v>
       </c>
       <c r="R4" t="n">
-        <v>6373460</v>
+        <v>6373483</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819042</v>
+        <v>123819055</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>4778</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497190</v>
+        <v>497235</v>
       </c>
       <c r="R5" t="n">
-        <v>6373593</v>
+        <v>6373313</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819049</v>
+        <v>123819054</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>5196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1100,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497080</v>
+        <v>497222</v>
       </c>
       <c r="R6" t="n">
-        <v>6373345</v>
+        <v>6373306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819045</v>
+        <v>123819040</v>
       </c>
       <c r="B7" t="n">
-        <v>95345</v>
+        <v>5176</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1211,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497270</v>
+        <v>497225</v>
       </c>
       <c r="R7" t="n">
-        <v>6373300</v>
+        <v>6373525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819041</v>
+        <v>123819045</v>
       </c>
       <c r="B8" t="n">
-        <v>91632</v>
+        <v>95345</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1342,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497150</v>
+        <v>497270</v>
       </c>
       <c r="R8" t="n">
-        <v>6373570</v>
+        <v>6373300</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819043</v>
+        <v>123819050</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>74893</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497237</v>
+        <v>497232</v>
       </c>
       <c r="R9" t="n">
-        <v>6373460</v>
+        <v>6373400</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819054</v>
+        <v>123819042</v>
       </c>
       <c r="B10" t="n">
-        <v>5196</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,39 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497222</v>
+        <v>497190</v>
       </c>
       <c r="R10" t="n">
-        <v>6373306</v>
+        <v>6373593</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819040</v>
+        <v>123819044</v>
       </c>
       <c r="B11" t="n">
-        <v>5176</v>
+        <v>105117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,39 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497225</v>
+        <v>497237</v>
       </c>
       <c r="R11" t="n">
-        <v>6373525</v>
+        <v>6373460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819055</v>
+        <v>123819043</v>
       </c>
       <c r="B12" t="n">
-        <v>4778</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,39 +1726,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497235</v>
+        <v>497237</v>
       </c>
       <c r="R12" t="n">
-        <v>6373313</v>
+        <v>6373460</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819050</v>
+        <v>123819048</v>
       </c>
       <c r="B13" t="n">
-        <v>74893</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497232</v>
+        <v>497275</v>
       </c>
       <c r="R13" t="n">
-        <v>6373400</v>
+        <v>6373290</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 10372-2025 artfynd.xlsx
+++ b/artfynd/A 10372-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819041</v>
+        <v>123819042</v>
       </c>
       <c r="B2" t="n">
-        <v>91632</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497150</v>
+        <v>497190</v>
       </c>
       <c r="R2" t="n">
-        <v>6373570</v>
+        <v>6373593</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819039</v>
+        <v>123819054</v>
       </c>
       <c r="B4" t="n">
-        <v>74885</v>
+        <v>5196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497240</v>
+        <v>497222</v>
       </c>
       <c r="R4" t="n">
-        <v>6373483</v>
+        <v>6373306</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819055</v>
+        <v>123819044</v>
       </c>
       <c r="B5" t="n">
-        <v>4778</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497235</v>
+        <v>497237</v>
       </c>
       <c r="R5" t="n">
-        <v>6373313</v>
+        <v>6373460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819054</v>
+        <v>123819041</v>
       </c>
       <c r="B6" t="n">
-        <v>5196</v>
+        <v>91632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,42 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497222</v>
+        <v>497150</v>
       </c>
       <c r="R6" t="n">
-        <v>6373306</v>
+        <v>6373570</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819040</v>
+        <v>123819055</v>
       </c>
       <c r="B7" t="n">
-        <v>5176</v>
+        <v>4778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,27 +1206,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497225</v>
+        <v>497235</v>
       </c>
       <c r="R7" t="n">
-        <v>6373525</v>
+        <v>6373313</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819045</v>
+        <v>123819050</v>
       </c>
       <c r="B8" t="n">
-        <v>95345</v>
+        <v>74893</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497270</v>
+        <v>497232</v>
       </c>
       <c r="R8" t="n">
-        <v>6373300</v>
+        <v>6373400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819050</v>
+        <v>123819045</v>
       </c>
       <c r="B9" t="n">
-        <v>74893</v>
+        <v>95345</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497232</v>
+        <v>497270</v>
       </c>
       <c r="R9" t="n">
-        <v>6373400</v>
+        <v>6373300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819042</v>
+        <v>123819043</v>
       </c>
       <c r="B10" t="n">
         <v>90977</v>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497190</v>
+        <v>497237</v>
       </c>
       <c r="R10" t="n">
-        <v>6373593</v>
+        <v>6373460</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819044</v>
+        <v>123819048</v>
       </c>
       <c r="B11" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497237</v>
+        <v>497275</v>
       </c>
       <c r="R11" t="n">
-        <v>6373460</v>
+        <v>6373290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819043</v>
+        <v>123819040</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>5176</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,34 +1721,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497237</v>
+        <v>497225</v>
       </c>
       <c r="R12" t="n">
-        <v>6373460</v>
+        <v>6373525</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819048</v>
+        <v>123819039</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>74885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497275</v>
+        <v>497240</v>
       </c>
       <c r="R13" t="n">
-        <v>6373290</v>
+        <v>6373483</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 10372-2025 artfynd.xlsx
+++ b/artfynd/A 10372-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819042</v>
+        <v>123819049</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497190</v>
+        <v>497080</v>
       </c>
       <c r="R2" t="n">
-        <v>6373593</v>
+        <v>6373345</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819049</v>
+        <v>123819054</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>5196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497080</v>
+        <v>497222</v>
       </c>
       <c r="R3" t="n">
-        <v>6373345</v>
+        <v>6373306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819054</v>
+        <v>123819044</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497222</v>
+        <v>497237</v>
       </c>
       <c r="R4" t="n">
-        <v>6373306</v>
+        <v>6373460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819044</v>
+        <v>123819055</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>4778</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497237</v>
+        <v>497235</v>
       </c>
       <c r="R5" t="n">
-        <v>6373460</v>
+        <v>6373313</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819041</v>
+        <v>123819050</v>
       </c>
       <c r="B6" t="n">
-        <v>91632</v>
+        <v>74893</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497150</v>
+        <v>497232</v>
       </c>
       <c r="R6" t="n">
-        <v>6373570</v>
+        <v>6373400</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819055</v>
+        <v>123819045</v>
       </c>
       <c r="B7" t="n">
-        <v>4778</v>
+        <v>95345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjunnaryd, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497235</v>
+        <v>497270</v>
       </c>
       <c r="R7" t="n">
-        <v>6373313</v>
+        <v>6373300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819050</v>
+        <v>123819043</v>
       </c>
       <c r="B8" t="n">
-        <v>74893</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497232</v>
+        <v>497237</v>
       </c>
       <c r="R8" t="n">
-        <v>6373400</v>
+        <v>6373460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819045</v>
+        <v>123819048</v>
       </c>
       <c r="B9" t="n">
-        <v>95345</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497270</v>
+        <v>497275</v>
       </c>
       <c r="R9" t="n">
-        <v>6373300</v>
+        <v>6373290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819043</v>
+        <v>123819039</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>74885</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497237</v>
+        <v>497240</v>
       </c>
       <c r="R10" t="n">
-        <v>6373460</v>
+        <v>6373483</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,317 +1600,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>123819048</v>
-      </c>
-      <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tjunnaryd, Sm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>497275</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6373290</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Vetlanda</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Björkö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>123819040</v>
-      </c>
-      <c r="B12" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Tjunnaryd, Sm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>497225</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6373525</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Vetlanda</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Björkö</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>123819039</v>
-      </c>
-      <c r="B13" t="n">
-        <v>74885</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6439</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Gulnål</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Tjunnaryd, Sm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>497240</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6373483</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Vetlanda</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Björkö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
